--- a/client/public/MasterTemplateCalendar.xlsx
+++ b/client/public/MasterTemplateCalendar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jod/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9980855D-B7D8-C34C-85D8-18B717021803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC15E10-F5D1-994B-B01C-9D79DDA136E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7760" yWindow="1500" windowWidth="30640" windowHeight="18580" xr2:uid="{D5D48D73-F2B6-4043-862B-1574BDD1879A}"/>
+    <workbookView xWindow="4360" yWindow="680" windowWidth="30200" windowHeight="20380" xr2:uid="{D5D48D73-F2B6-4043-862B-1574BDD1879A}"/>
   </bookViews>
   <sheets>
     <sheet name="Current-EH-PH-SH-Kids-26062026" sheetId="1" r:id="rId1"/>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="48">
-  <si>
-    <t>Master Rotation Template - Family and Work — 4 weekly cycle combining EH, PH, SH, Kids</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
   <si>
     <t>Last revision:</t>
   </si>
@@ -50,9 +47,6 @@
     <t>Key:</t>
   </si>
   <si>
-    <t>EH = Elgin House, SH = Sandringham, PH = Peninsula, Kids = Kids with us</t>
-  </si>
-  <si>
     <t>Starting week as per week 1 of SH week cycle:</t>
   </si>
   <si>
@@ -66,9 +60,6 @@
   </si>
   <si>
     <t>PH week</t>
-  </si>
-  <si>
-    <t>Kids week</t>
   </si>
   <si>
     <t>Mon</t>
@@ -108,15 +99,6 @@
     <t>SH: Gynae OT</t>
   </si>
   <si>
-    <t>Kids</t>
-  </si>
-  <si>
-    <t>Kids with us</t>
-  </si>
-  <si>
-    <t>Kids handover 0900</t>
-  </si>
-  <si>
     <t>Week 2</t>
   </si>
   <si>
@@ -125,9 +107,6 @@
   <si>
     <t>PH: UROGYN (AM) / 
 GEN GYN (PM)</t>
-  </si>
-  <si>
-    <t>Kids handover 1500</t>
   </si>
   <si>
     <t>Week 3</t>
@@ -207,10 +186,10 @@
     <t>Work Links</t>
   </si>
   <si>
-    <t xml:space="preserve">Source for Master Rotation Template Document: </t>
-  </si>
-  <si>
-    <t>MasterTemplateCalendar.xlsx</t>
+    <t>EH = Elgin House, SH = Sandringham, PH = Peninsula</t>
+  </si>
+  <si>
+    <t>Master Rotation Template -Work - 4 weekly cycle combining EH, PH, SH</t>
   </si>
 </sst>
 </file>
@@ -325,7 +304,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -438,77 +417,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -523,9 +437,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -553,19 +464,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -586,7 +484,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -891,448 +789,315 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32B225F7-FDF9-294A-A431-4E93FC310A03}">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.1640625" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
     <col min="3" max="3" width="10.5" style="4" customWidth="1"/>
-    <col min="4" max="5" width="10" customWidth="1"/>
-    <col min="6" max="6" width="13.6640625" customWidth="1"/>
-    <col min="7" max="7" width="17.1640625" customWidth="1"/>
-    <col min="8" max="8" width="41.83203125" customWidth="1"/>
-    <col min="9" max="10" width="15.6640625" customWidth="1"/>
-    <col min="11" max="12" width="14.1640625" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.1640625" customWidth="1"/>
+    <col min="7" max="7" width="41.83203125" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="11" width="14.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+    </row>
+    <row r="2" spans="1:11" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-    </row>
-    <row r="2" spans="1:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="B2" s="3">
         <v>46199</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-    </row>
-    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="35" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B4" s="6">
+        <v>46258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7">
-        <v>46202</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="35" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="G5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="H5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="J5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="K5" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="9" t="s">
+    </row>
+    <row r="6" spans="1:11" ht="32" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <f>B4</f>
+        <v>46258</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="C6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="E6" s="12" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="31" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="12">
-        <f>B4</f>
-        <v>46202</v>
-      </c>
-      <c r="B7" s="13" t="s">
+      <c r="F6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="H6" s="12"/>
+      <c r="I6" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="13" t="s">
+      <c r="J6" s="12"/>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="1:11" ht="31" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <f>B4+7</f>
+        <v>46265</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="C7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="D7" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13" t="s">
+      <c r="F7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>21</v>
       </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="12"/>
       <c r="K7" s="13"/>
-      <c r="L7" s="14"/>
-    </row>
-    <row r="8" spans="1:12" ht="33" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="18" t="s">
+    </row>
+    <row r="8" spans="1:11" ht="33" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <f>B4+14</f>
+        <v>46272</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="C8" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="19" t="s">
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="13"/>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" s="11">
+        <f>B4+21</f>
+        <v>46279</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="L8" s="20"/>
-    </row>
-    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="12">
-        <f>B4+7</f>
-        <v>46209</v>
-      </c>
-      <c r="B9" s="13" t="s">
+      <c r="H9" s="12"/>
+      <c r="I9" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="13"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+    </row>
+    <row r="11" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="A11" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" s="13" t="s">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="15" t="s">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="14"/>
-    </row>
-    <row r="10" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="17" t="s">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="L10" s="18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="32" x14ac:dyDescent="0.2">
-      <c r="A11" s="12">
-        <f>B4+14</f>
-        <v>46216</v>
-      </c>
-      <c r="B11" s="13" t="s">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="21"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H11" s="21" t="s">
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="14"/>
-    </row>
-    <row r="12" spans="1:12" ht="33" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="20"/>
-    </row>
-    <row r="13" spans="1:12" ht="30" x14ac:dyDescent="0.2">
-      <c r="A13" s="12">
-        <f>B4+21</f>
-        <v>46223</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="15" t="s">
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" s="13"/>
-      <c r="L13" s="14"/>
-    </row>
-    <row r="14" spans="1:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-    </row>
-    <row r="16" spans="1:12" ht="24" x14ac:dyDescent="0.3">
-      <c r="A16" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="26" t="s">
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" s="21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" s="21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" s="21"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" s="21" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="27" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="27" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="27" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="27"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="26" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="26" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" s="27" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" s="27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" s="27" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" s="27"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="27" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A18" r:id="rId1" location="/launchitemsv2" tooltip="https://phworkspace.cloud.com" xr:uid="{1D2DC4E2-1084-8441-AC5C-C149583F7F3E}"/>
-    <hyperlink ref="A19" r:id="rId2" tooltip="Original URL:_x000a_https://phcnvicgovau.sharepoint.com/:f:/r/sites/PeninsulaWomensMedicalStaff-SeniorMedicalStaff/Shared%20Documents/Senior%20Medical%20Staff/Rosters/On%20Call%20Rosters/2025?csf=1&amp;web=1&amp;e=KBMez0_x000a__x000a_Click to follow link." display="https://phcnvicgovau.sharepoint.com/:f:/r/sites/PeninsulaWomensMedicalStaff-SeniorMedicalStaff/Shared Documents/Senior Medical Staff/Rosters/On Call Rosters/2025?csf=1&amp;web=1&amp;e=KBMez0" xr:uid="{E25A7E3C-70BD-2846-8E6F-142C209D417A}"/>
-    <hyperlink ref="A20" r:id="rId3" tooltip="https://www.mypeninsulacme.org/" display="https://www.mypeninsulacme.org/" xr:uid="{649B54A2-0004-6646-96BA-157748CACCEF}"/>
-    <hyperlink ref="A28" r:id="rId4" tooltip="https://docs.google.com/spreadsheets/d/e/2PACX-1vTSzjuRBimGQeD-JYWhombqZCVO_mi1Wa3XBk5GBn8_sb44_w3qVPoBtguWDS2kFZ3yqSrFvZewkhjj/pubhtml" display="https://docs.google.com/spreadsheets/d/e/2PACX-1vTSzjuRBimGQeD-JYWhombqZCVO_mi1Wa3XBk5GBn8_sb44_w3qVPoBtguWDS2kFZ3yqSrFvZewkhjj/pubhtml" xr:uid="{97103497-3217-6542-9C89-90700A6F5035}"/>
-    <hyperlink ref="A33" r:id="rId5" tooltip="https://docs.google.com/spreadsheets/d/e/2PACX-1vQj1ryZ2bODLhWhGrvdEGxqkvV2xU7U6Llak8ddIygDpQ4Szo61Sklcx9Z80i4R1w/pubhtml#" display="https://docs.google.com/spreadsheets/d/e/2PACX-1vQj1ryZ2bODLhWhGrvdEGxqkvV2xU7U6Llak8ddIygDpQ4Szo61Sklcx9Z80i4R1w/pubhtml" xr:uid="{CF459C2A-B7E8-7044-9405-BC46799BA84B}"/>
-    <hyperlink ref="A29" r:id="rId6" tooltip="https://docs.google.com/spreadsheets/d/e/2PACX-1vTG30YbRcKl46c7S_iF5stnqWC7RcVD86urXMM2zKL-d_PncJ4ggvF7OksLo5KDwA/pubhtml" display="https://docs.google.com/spreadsheets/d/e/2PACX-1vTG30YbRcKl46c7S_iF5stnqWC7RcVD86urXMM2zKL-d_PncJ4ggvF7OksLo5KDwA/pubhtml" xr:uid="{EEDC966F-584D-3443-9BDB-4A5F6FC78C86}"/>
-    <hyperlink ref="A27" r:id="rId7" tooltip="https://docs.google.com/document/d/1dd_UlL7Fjpv1VSW4uL0gE_xW1pJQrNb0vqXH_JeOYzo/edit?tab=t.0" display="https://docs.google.com/document/d/1dd_UlL7Fjpv1VSW4uL0gE_xW1pJQrNb0vqXH_JeOYzo/edit?tab=t.0" xr:uid="{A778CF2F-06AE-E944-94A2-1E885AB792CE}"/>
-    <hyperlink ref="A30" r:id="rId8" xr:uid="{5D68DDF5-99FB-C743-88F7-CA80E674AB8D}"/>
-    <hyperlink ref="A31" r:id="rId9" display="Monash Remove Access" xr:uid="{5F83D27A-3F7C-8F4F-9CB1-E332E622EB4F}"/>
-    <hyperlink ref="B5" r:id="rId10" display="https://aupfhs-my.sharepoint.com/:x:/g/personal/drjoliverdaly_aupfhs_com_au/IQDsUHLeUrNvT6s3TG-wnIR-AbWRZRI35CJRzfzcsk00xvo?e=YDmWgC" xr:uid="{FD8D5D8C-F7FD-7547-AF53-A2F54ECBCE61}"/>
+    <hyperlink ref="A13" r:id="rId1" location="/launchitemsv2" tooltip="https://phworkspace.cloud.com" xr:uid="{1D2DC4E2-1084-8441-AC5C-C149583F7F3E}"/>
+    <hyperlink ref="A14" r:id="rId2" tooltip="Original URL:_x000a_https://phcnvicgovau.sharepoint.com/:f:/r/sites/PeninsulaWomensMedicalStaff-SeniorMedicalStaff/Shared%20Documents/Senior%20Medical%20Staff/Rosters/On%20Call%20Rosters/2025?csf=1&amp;web=1&amp;e=KBMez0_x000a__x000a_Click to follow link." display="https://phcnvicgovau.sharepoint.com/:f:/r/sites/PeninsulaWomensMedicalStaff-SeniorMedicalStaff/Shared Documents/Senior Medical Staff/Rosters/On Call Rosters/2025?csf=1&amp;web=1&amp;e=KBMez0" xr:uid="{E25A7E3C-70BD-2846-8E6F-142C209D417A}"/>
+    <hyperlink ref="A15" r:id="rId3" tooltip="https://www.mypeninsulacme.org/" display="https://www.mypeninsulacme.org/" xr:uid="{649B54A2-0004-6646-96BA-157748CACCEF}"/>
+    <hyperlink ref="A23" r:id="rId4" tooltip="https://docs.google.com/spreadsheets/d/e/2PACX-1vTSzjuRBimGQeD-JYWhombqZCVO_mi1Wa3XBk5GBn8_sb44_w3qVPoBtguWDS2kFZ3yqSrFvZewkhjj/pubhtml" display="https://docs.google.com/spreadsheets/d/e/2PACX-1vTSzjuRBimGQeD-JYWhombqZCVO_mi1Wa3XBk5GBn8_sb44_w3qVPoBtguWDS2kFZ3yqSrFvZewkhjj/pubhtml" xr:uid="{97103497-3217-6542-9C89-90700A6F5035}"/>
+    <hyperlink ref="A28" r:id="rId5" tooltip="https://docs.google.com/spreadsheets/d/e/2PACX-1vQj1ryZ2bODLhWhGrvdEGxqkvV2xU7U6Llak8ddIygDpQ4Szo61Sklcx9Z80i4R1w/pubhtml#" display="https://docs.google.com/spreadsheets/d/e/2PACX-1vQj1ryZ2bODLhWhGrvdEGxqkvV2xU7U6Llak8ddIygDpQ4Szo61Sklcx9Z80i4R1w/pubhtml" xr:uid="{CF459C2A-B7E8-7044-9405-BC46799BA84B}"/>
+    <hyperlink ref="A24" r:id="rId6" tooltip="https://docs.google.com/spreadsheets/d/e/2PACX-1vTG30YbRcKl46c7S_iF5stnqWC7RcVD86urXMM2zKL-d_PncJ4ggvF7OksLo5KDwA/pubhtml" display="https://docs.google.com/spreadsheets/d/e/2PACX-1vTG30YbRcKl46c7S_iF5stnqWC7RcVD86urXMM2zKL-d_PncJ4ggvF7OksLo5KDwA/pubhtml" xr:uid="{EEDC966F-584D-3443-9BDB-4A5F6FC78C86}"/>
+    <hyperlink ref="A22" r:id="rId7" tooltip="https://docs.google.com/document/d/1dd_UlL7Fjpv1VSW4uL0gE_xW1pJQrNb0vqXH_JeOYzo/edit?tab=t.0" display="https://docs.google.com/document/d/1dd_UlL7Fjpv1VSW4uL0gE_xW1pJQrNb0vqXH_JeOYzo/edit?tab=t.0" xr:uid="{A778CF2F-06AE-E944-94A2-1E885AB792CE}"/>
+    <hyperlink ref="A25" r:id="rId8" xr:uid="{5D68DDF5-99FB-C743-88F7-CA80E674AB8D}"/>
+    <hyperlink ref="A26" r:id="rId9" display="Monash Remove Access" xr:uid="{5F83D27A-3F7C-8F4F-9CB1-E332E622EB4F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
